--- a/02_加值成品/八上/八上4-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上4-3_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上4-3 光與顏色　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國二上學期 八上4-3 光與顏色　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>白光經稜鏡分成七彩稱？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>白光</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>色散</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>青色</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>該顏色</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>分光</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>光的三原色是？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>紅綠藍</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>暗(相減)</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>紅光</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>近黑色</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>RGB</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>三原色光混合成？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>青色</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>該顏色</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>白光</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>相加</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>紅蘋果反射什麼光？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>紅光</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>白光</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>全吸收</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>水滴色散陽光</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>吸其他</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>白色物體對色光如何？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>紅光</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>色散</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>紫光</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>全反射</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>看似白</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>黑色物體對色光如何？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>全吸收</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>紅光</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>紫光</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>看似黑</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>色散中偏折最大的是？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>紅光</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>全反射</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>紫光</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>色散</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>折射大</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>彩虹是什麼造成？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>該顏色</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>水滴色散陽光</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>近黑色</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>紅色</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>自然色散</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>太陽光是單色光還混合光？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>紅綠藍</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>混合光</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>紫光</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>紅光</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>含多色</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>物體反射某色光我們就看到它為？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>該顏色</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>色散</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>青色</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>白光</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>反射色</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上4-3 光與顏色　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國二上學期 八上4-3 光與顏色　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>綠葉為何是綠色？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>反射綠光吸收其他</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>紅折射小偏折少排最外</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>涵蓋可見光讓眼感白</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>不同氣體發不同色光</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>反射色</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>紅光照白紙看到？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>紅色</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>暗(相減)</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>全反射</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>反射紅光</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>紅光照綠葉看到？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>全吸收</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>混合光</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>紫光</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>近黑色</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>綠葉不反射紅</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>紅+綠光混合得？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>紅色</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>紅綠藍</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>黃光</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>該顏色</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>相加</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>顏料紅+綠混合偏？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>紅色</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>紅綠藍</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>暗(相減)</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>色散</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>吸收多</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>偏折最小的色光是？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>全反射</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>近黑色</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>紅光</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>折射小</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>螢幕用哪三色顯像？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>白光</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>紅色</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>紅綠藍</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>紫光</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>RGB</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>藍+綠光混合得？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>紅光</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>色散</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>青色</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>白光</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>相加</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>香蕉呈黃色因為反射？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>黃光</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>混合光</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>白光</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>紫光</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>反射</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>紅綠藍三色光等量疊加成？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>白光</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>暗(相減)</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>色散</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>相加</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上4-3 光與顏色　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國二上學期 八上4-3 光與顏色　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>白襯衫在紅燈下呈？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>色散</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>紅光</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>紅綠藍</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>紅色</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>反射照入的紅光</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>為何色光是加法、顏料是減法？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>紅折射小偏折少排最外</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>吸收較多光轉熱</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>青洋紅黃(CMY)</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>色光疊加能量增；顏料吸收特定光</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>機制</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>紅花在只有藍光房間呈？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>黑色</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>混合光</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>紫光</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>色散</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>無紅光可反射</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>三原色光等量混合為何是白？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>反射綠光吸收其他</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>色光疊加能量增；顏料吸收特定光</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>涵蓋可見光讓眼感白</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>陽光經水滴折射與色散</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>混色</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>彩虹紅在外紫在內原因？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>紅折射小偏折少排最外</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>吸收較多光轉熱</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>陽光經水滴折射與色散</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>色光疊加能量增；顏料吸收特定光</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>色散</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>黑衣夏天較熱因為？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>吸收較多光轉熱</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>紅折射小偏折少排最外</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>不同氣體發不同色光</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>色光疊加能量增；顏料吸收特定光</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>吸收</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>印表機用何顏料三原色？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>不同氣體發不同色光</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>反射綠光吸收其他</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>陽光經水滴折射與色散</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>青洋紅黃(CMY)</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>相減</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>霓虹招牌各色靠什麼？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>陽光經水滴折射與色散</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>紅折射小偏折少排最外</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>反射綠光吸收其他</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>不同氣體發不同色光</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>發光</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>雨後彩虹的成因？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>陽光經水滴折射與色散</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>青洋紅黃(CMY)</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>色光疊加能量增；顏料吸收特定光</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>吸收較多光轉熱</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>色散</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>不同色燈打在白衣上白衣呈？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>暗(相減)</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>燈的顏色</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>混合光</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>水滴色散陽光</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>反射</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/八上/八上4-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上4-3_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>分光</t>
+          <t>分光：白光其實是由多種顏色的光混合而成，經過稜鏡時各色光偏折角度不同而被分開，這個現象稱為色散</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>RGB</t>
+          <t>RGB：色光的三原色是紅、綠、藍，混合這三種色光可以組合出大部分顏色</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>相加</t>
+          <t>相加：把紅、綠、藍三種色光以適當比例等量疊加在一起，會產生白光，這是色光的相加混色</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>吸其他</t>
+          <t>吸其他：紅蘋果表皮吸收了大部分其他顏色的光，只反射紅色光進入我們眼睛，所以看起來是紅色的</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>看似白</t>
+          <t>看似白：白色物體幾乎能反射所有顏色的色光，因此看起來呈現白色</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>看似黑</t>
+          <t>看似黑：黑色物體幾乎能吸收所有顏色的色光、不反射，因此看起來呈現黑色</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>折射大</t>
+          <t>折射大：白光經過稜鏡色散時，紫光偏折的角度最大，紅光偏折角度最小</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>自然色散</t>
+          <t>自然色散：雨後空氣中懸浮的小水滴，使陽光發生折射與色散，再經內部反射射出，就形成了彩虹</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>含多色</t>
+          <t>含多色：太陽光其實是由紅橙黃綠藍靛紫等多種色光混合而成的混合光，經過三稜鏡可以分散成七彩</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>反射色</t>
+          <t>反射色：物體本身不發光，我們看到物體呈現什麼顏色，是因為它反射了該顏色的光進入我們眼睛</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>反射色</t>
+          <t>反射色：葉子中的葉綠素吸收了大部分其他顏色的光，只反射綠色光，所以葉子看起來是綠色的</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>反射紅光</t>
+          <t>反射紅光：白紙能反射各種顏色的光，只照紅光時，白紙只能反射這唯一的紅光，所以看到紅色</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>綠葉不反射紅</t>
+          <t>綠葉不反射紅：綠葉只反射綠光、不太反射紅光，用紅光照射時幾乎沒有光可以反射進眼睛，所以看起來接近黑色</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>相加</t>
+          <t>相加：紅光和綠光以適當比例疊加(相加混色)會產生黃光</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>吸收多</t>
+          <t>吸收多：顏料混合是靠相減混色，紅色顏料和綠色顏料混合後，能吸收的光波段變多，反射出來的光變少，顏色會偏暗濁</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>折射小</t>
+          <t>折射小：白光經過稜鏡色散時，紅光偏折的角度最小，紫光偏折角度最大</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>RGB</t>
+          <t>RGB：螢幕用紅、綠、藍三種色光小點組合，靠相加混色顯示出各種顏色</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>相加</t>
+          <t>相加：藍光和綠光以適當比例疊加(相加混色)會產生青色</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>反射</t>
+          <t>反射：香蕉表皮吸收了大部分其他顏色的光，只反射黃色光進入我們眼睛，所以看起來是黃色的</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>相加</t>
+          <t>相加：色光的三原色是紅、綠、藍，把這三種色光以適當比例等量疊加在一起會產生白光</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>反射照入的紅光</t>
+          <t>反射照入的紅光：白色物體能反射照射到它身上的各種色光，在只有紅燈的環境下，白襯衫只能反射唯一存在的紅光，所以看起來呈現紅色</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>機制</t>
+          <t>機制：色光混合是不同波長的光疊加在一起，能量(亮度)越疊越多，所以是加法混色；顏料混合則是每種顏料吸收特定波段的光，混合的顏料種類越多，被吸收掉的光波段也越多，剩下反射的光越少，所以是減法混色</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>無紅光可反射</t>
+          <t>無紅光可反射：紅花只能反射紅色光，在只有藍光的房間裡沒有紅光可供反射，紅花因此幾乎不反射任何光，看起來呈現黑色</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>混色</t>
+          <t>混色：紅、綠、藍三種色光的波長範圍剛好能涵蓋人眼可感知的大部分可見光範圍，等量混合疊加後，眼睛感受到的就是白光</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>色散</t>
+          <t>色散：色散時紅光偏折角度最小、紫光偏折角度最大，偏折角度小的紅光落在彩虹外側，偏折角度大的紫光落在內側，所以彩虹紅在外、紫在內</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>吸收</t>
+          <t>吸收：黑色衣服幾乎吸收所有顏色的光、不太反射，吸收的光能大部分轉換成熱能，使衣服和身體溫度升高，所以夏天穿黑衣感覺較熱</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>相減</t>
+          <t>相減：印表機的顏料採用相減混色原理，用青、洋紅、黃三種顏料為三原色，透過不同比例疊印吸收不同的光，組合出各種顏色</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>發光</t>
+          <t>發光：霓虹燈管內填充不同種類的氣體，通電後每種氣體會發出各自特定顏色的光，因此能組成五顏六色的招牌</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>色散</t>
+          <t>色散：雨後空氣中懸浮著許多小水滴，陽光進入水滴時發生折射，不同顏色的光偏折角度不同(色散)，再經水滴內部反射後射出，就形成了我們看到的彩虹</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>反射</t>
+          <t>反射：白色衣服本身能反射各種顏色的光，所以照到什麼顏色的燈光，白衣服就會反射出那個顏色，看起來呈現燈光的顏色</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/八上/八上4-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上4-3_三種難度測驗卷.xlsx
@@ -563,7 +563,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>白光</t>
+          <t>燈的顏色</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -573,12 +573,12 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>青色</t>
+          <t>紅綠藍</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>該顏色</t>
+          <t>黃光</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>該顏色</t>
+          <t>紫光</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -853,12 +853,12 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>近黑色</t>
+          <t>燈的顏色</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>紅色</t>
+          <t>紅光</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
@@ -1119,17 +1119,17 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>全吸收</t>
+          <t>燈的顏色</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>混合光</t>
+          <t>暗(相減)</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>紫光</t>
+          <t>水滴色散陽光</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -1600,17 +1600,17 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>混合光</t>
+          <t>紅光</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>紫光</t>
+          <t>該顏色</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>色散</t>
+          <t>紅綠藍</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
